--- a/artfynd/A 31606-2026 artfynd.xlsx
+++ b/artfynd/A 31606-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136152651</v>
       </c>
       <c r="B2" t="n">
-        <v>89468</v>
+        <v>89470</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136152663</v>
       </c>
       <c r="B3" t="n">
-        <v>89468</v>
+        <v>89470</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136152691</v>
       </c>
       <c r="B4" t="n">
-        <v>92455</v>
+        <v>92458</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1020,7 +1020,7 @@
         <v>136152654</v>
       </c>
       <c r="B5" t="n">
-        <v>93072</v>
+        <v>93075</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -3737,7 +3737,7 @@
         <v>136152653</v>
       </c>
       <c r="B28" t="n">
-        <v>110087</v>
+        <v>110090</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>

--- a/artfynd/A 31606-2026 artfynd.xlsx
+++ b/artfynd/A 31606-2026 artfynd.xlsx
@@ -907,7 +907,7 @@
         <v>136152691</v>
       </c>
       <c r="B4" t="n">
-        <v>92458</v>
+        <v>92459</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1020,7 +1020,7 @@
         <v>136152654</v>
       </c>
       <c r="B5" t="n">
-        <v>93075</v>
+        <v>93076</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -3737,7 +3737,7 @@
         <v>136152653</v>
       </c>
       <c r="B28" t="n">
-        <v>110090</v>
+        <v>110091</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>

--- a/artfynd/A 31606-2026 artfynd.xlsx
+++ b/artfynd/A 31606-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136152651</v>
       </c>
       <c r="B2" t="n">
-        <v>89470</v>
+        <v>89472</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136152663</v>
       </c>
       <c r="B3" t="n">
-        <v>89470</v>
+        <v>89472</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136152691</v>
       </c>
       <c r="B4" t="n">
-        <v>92459</v>
+        <v>92464</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1020,7 +1020,7 @@
         <v>136152654</v>
       </c>
       <c r="B5" t="n">
-        <v>93076</v>
+        <v>93081</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1133,7 +1133,7 @@
         <v>136152650</v>
       </c>
       <c r="B6" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1250,7 +1250,7 @@
         <v>136152658</v>
       </c>
       <c r="B7" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1367,7 +1367,7 @@
         <v>136152661</v>
       </c>
       <c r="B8" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1484,7 +1484,7 @@
         <v>136152664</v>
       </c>
       <c r="B9" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1601,7 +1601,7 @@
         <v>136152667</v>
       </c>
       <c r="B10" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1718,7 +1718,7 @@
         <v>136152669</v>
       </c>
       <c r="B11" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1835,7 +1835,7 @@
         <v>136152671</v>
       </c>
       <c r="B12" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1952,7 +1952,7 @@
         <v>136152673</v>
       </c>
       <c r="B13" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2069,7 +2069,7 @@
         <v>136152675</v>
       </c>
       <c r="B14" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2186,7 +2186,7 @@
         <v>136152676</v>
       </c>
       <c r="B15" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2303,7 +2303,7 @@
         <v>136152677</v>
       </c>
       <c r="B16" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2420,7 +2420,7 @@
         <v>136152681</v>
       </c>
       <c r="B17" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2537,7 +2537,7 @@
         <v>136152683</v>
       </c>
       <c r="B18" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2654,7 +2654,7 @@
         <v>136152684</v>
       </c>
       <c r="B19" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2771,7 +2771,7 @@
         <v>136152687</v>
       </c>
       <c r="B20" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2888,7 +2888,7 @@
         <v>136152688</v>
       </c>
       <c r="B21" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3005,7 +3005,7 @@
         <v>136152655</v>
       </c>
       <c r="B22" t="n">
-        <v>58006</v>
+        <v>58008</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3127,7 +3127,7 @@
         <v>136152660</v>
       </c>
       <c r="B23" t="n">
-        <v>58006</v>
+        <v>58008</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3249,7 +3249,7 @@
         <v>136152668</v>
       </c>
       <c r="B24" t="n">
-        <v>58006</v>
+        <v>58008</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3371,7 +3371,7 @@
         <v>136152674</v>
       </c>
       <c r="B25" t="n">
-        <v>58006</v>
+        <v>58008</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3493,7 +3493,7 @@
         <v>136152685</v>
       </c>
       <c r="B26" t="n">
-        <v>58006</v>
+        <v>58008</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3615,7 +3615,7 @@
         <v>136152686</v>
       </c>
       <c r="B27" t="n">
-        <v>58006</v>
+        <v>58008</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3737,7 +3737,7 @@
         <v>136152653</v>
       </c>
       <c r="B28" t="n">
-        <v>110091</v>
+        <v>110096</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
